--- a/dados/Estação - status 2025_05_30 (1).xlsx
+++ b/dados/Estação - status 2025_05_30 (1).xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://incorporadoraampla-my.sharepoint.com/personal/vitor_amplaincorporadora_com_br/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://incorporadoraampla.sharepoint.com/sites/Controladoria/Documentos Compartilhados/amplaGitHub/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{557D122D-0488-4809-AA68-F085EC2F11C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:20001_{557D122D-0488-4809-AA68-F085EC2F11C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F45A875E-D2FF-46C6-9BB7-4D447C32F5BA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{240890F9-D451-4B7D-B96D-9A56BDF9E0C9}"/>
+    <workbookView xWindow="-43155" yWindow="-3555" windowWidth="14355" windowHeight="15600" activeTab="1" xr2:uid="{240890F9-D451-4B7D-B96D-9A56BDF9E0C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Estação" sheetId="1" r:id="rId1"/>
     <sheet name="DRE gerencial" sheetId="4" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -262,7 +258,7 @@
     <numFmt numFmtId="42" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$R$-416]\ * #,##0_-;\-[$R$-416]\ * #,##0_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$R$-416]\ * #,##0_-;\-[$R$-416]\ * #,##0_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -360,7 +356,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -379,23 +375,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -425,6 +419,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="32" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <strike val="0"/>
@@ -438,9 +435,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="32" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -464,78 +458,12 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="3bb659e6-52d1-4a59-9c5b-210dde6"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="10">
-          <cell r="T10">
-            <v>3928182.12</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="DRE Finc"/>
-      <sheetName val="Demonstrativo Eco-Finc"/>
-      <sheetName val="Fluxo"/>
-      <sheetName val="Matriz MCMV"/>
-      <sheetName val="Matriz"/>
-      <sheetName val="CurvaObra"/>
-      <sheetName val="CurvaVenda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="34">
-          <cell r="E34">
-            <v>58847199.720000006</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="E76">
-            <v>56633497.8864685</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="E79">
-            <v>34309815.140000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2A349DC-E756-4DF7-B9FC-B9380BCF9FFD}" name="Tabela1" displayName="Tabela1" ref="A1:F16" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:F16" xr:uid="{F2A349DC-E756-4DF7-B9FC-B9380BCF9FFD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F45AFD39-9BD8-4DBE-8C33-CEC4A94BA852}" name="Variável" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{0E743F29-CE0F-479A-8A74-06568B1A78E2}" name="Valor" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{F45AFD39-9BD8-4DBE-8C33-CEC4A94BA852}" name="Variável" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{0E743F29-CE0F-479A-8A74-06568B1A78E2}" name="Valor" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{63CA617D-416F-4841-BFF8-13E67BA82AA1}" name="Natureza"/>
     <tableColumn id="4" xr3:uid="{97EC728A-08AA-48B4-BCA6-70ABDDE9B795}" name="Status"/>
     <tableColumn id="5" xr3:uid="{21AF76FD-5DE1-490B-A0B0-67EAFBF8A356}" name="Fonte"/>
@@ -1177,7 +1105,6 @@
         <v>25</v>
       </c>
       <c r="B2" s="10">
-        <f>'[2]Demonstrativo Eco-Finc'!$E$34</f>
         <v>58847199.720000006</v>
       </c>
       <c r="C2" t="s">
@@ -1195,10 +1122,10 @@
       <c r="H2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="33">
+      <c r="I2" s="31">
         <v>1</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="26">
         <f>B2</f>
         <v>58847199.720000006</v>
       </c>
@@ -1211,7 +1138,6 @@
         <v>51</v>
       </c>
       <c r="B3" s="16">
-        <f>'[1]3bb659e6-52d1-4a59-9c5b-210dde6'!$T$10</f>
         <v>3928182.12</v>
       </c>
       <c r="C3" t="s">
@@ -1226,11 +1152,11 @@
       <c r="H3" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <f>SUM(B4:B8)/B2</f>
         <v>1.5063933466977208</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="25">
         <f>SUM(B4:B8)</f>
         <v>88647030.129999995</v>
       </c>
@@ -1366,29 +1292,28 @@
       <c r="H8" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="22">
         <f>SUM(B4:B5)/B2</f>
         <v>0.28974612948668615</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="23">
         <f>SUM(B4:B5)</f>
         <v>17050748.350000001</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="27">
         <f>SUM(B6:B8)/B2</f>
         <v>1.216647217211035</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="28">
         <f>SUM(B6:B8)</f>
         <v>71596281.780000001</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B9" s="10">
-        <f>'[2]Demonstrativo Eco-Finc'!$E$76</f>
         <v>56633497.8864685</v>
       </c>
       <c r="C9" t="s">
@@ -1403,29 +1328,27 @@
       <c r="H9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="24">
-        <f>B12/'[2]Demonstrativo Eco-Finc'!$E$79</f>
+      <c r="I9" s="22">
         <v>0.11177029034846615</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="23">
         <f>B12</f>
         <v>3834818</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="29">
         <f>B14/B10</f>
         <v>0.88822970965153381</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="30">
         <f>B14</f>
         <v>30474997.140000001</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="10">
-        <f>'[2]Demonstrativo Eco-Finc'!$E$79</f>
         <v>34309815.140000001</v>
       </c>
       <c r="C10" t="s">
@@ -1437,28 +1360,28 @@
       <c r="E10" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="22">
         <f>B13/B11</f>
         <v>0.44614639229163772</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="23">
         <f>B13</f>
         <v>9959630.5199999996</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="29">
         <f>B15/B11</f>
         <v>0.55385360770836234</v>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="30">
         <f>B15</f>
         <v>12364052.2264685</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B11" s="10">
@@ -1604,7 +1527,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:C2 B4:C16 C3">
+  <conditionalFormatting sqref="B2:C2 C3 B4:C16">
     <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>$C2="Saída"</formula>
     </cfRule>
@@ -1824,15 +1747,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5a5f483f-f768-438e-b4ef-63f46a7558dd">
@@ -1843,14 +1757,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4F0FA7-E385-4DF8-BB02-2E14BD59FC63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4F0FA7-E385-4DF8-BB02-2E14BD59FC63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5a5f483f-f768-438e-b4ef-63f46a7558dd"/>
+    <ds:schemaRef ds:uri="dd8c73df-45bd-468c-aae5-f3faedcbd5e2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50EC92D-BDE3-4863-955F-38F9F0060374}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3576F8A2-EA3D-4868-B462-521B28C98BF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5a5f483f-f768-438e-b4ef-63f46a7558dd"/>
+    <ds:schemaRef ds:uri="dd8c73df-45bd-468c-aae5-f3faedcbd5e2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3576F8A2-EA3D-4868-B462-521B28C98BF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50EC92D-BDE3-4863-955F-38F9F0060374}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>